--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3163,6 +3163,246 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123691696</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56824</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ebbegärde Kronopark, Ebbegärde Kronopark, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>574797</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6303215</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per-Göran Svensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per-Göran Svensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123691640</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58159</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ebbegärde Kronopark, Ebbegärde Kronopark, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>574797</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6303215</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per-Göran Svensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per-Göran Svensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -3168,7 +3168,7 @@
         <v>123691696</v>
       </c>
       <c r="B22" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>123691640</v>
       </c>
       <c r="B23" t="n">
-        <v>58159</v>
+        <v>58165</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -3168,7 +3168,7 @@
         <v>123691696</v>
       </c>
       <c r="B22" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>123691640</v>
       </c>
       <c r="B23" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115041353</v>
+        <v>115041303</v>
       </c>
       <c r="B14" t="n">
-        <v>57414</v>
+        <v>57206</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102622</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2247,6 +2247,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hördes mycket bra. 04.09 Korsningen Linjevägen- Ekebergsvägen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115041366</v>
+        <v>115041390</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
+        <v>56481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,20 +2290,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2315,7 +2320,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2373,6 +2378,11 @@
           <t>09:00</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tranevensvägen  vid jaktstuga  08.05</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2390,17 +2400,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per-Göran Svensson, Lars G Petersson</t>
+          <t>Per-Göran Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115041303</v>
+        <v>115041343</v>
       </c>
       <c r="B16" t="n">
-        <v>57206</v>
+        <v>57215</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2413,16 +2423,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102622</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2499,7 +2509,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hördes mycket bra. 04.09 Korsningen Linjevägen- Ekebergsvägen</t>
+          <t>Ebbegärdsvägen- Älvemossevägen  05.24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,10 +2536,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115041390</v>
+        <v>115516526</v>
       </c>
       <c r="B17" t="n">
-        <v>56481</v>
+        <v>57885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2538,20 +2548,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>103042</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2568,7 +2578,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2608,27 +2618,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tranevensvägen  vid jaktstuga  08.05</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,10 +2660,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115041343</v>
+        <v>115516506</v>
       </c>
       <c r="B18" t="n">
-        <v>57215</v>
+        <v>56478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2671,21 +2676,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2694,10 +2699,14 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2737,27 +2746,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ebbegärdsvägen- Älvemossevägen  05.24</t>
+          <t>Mellanvägen stod på vägen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2777,17 +2786,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per-Göran Svensson, Lars G Petersson</t>
+          <t>Per-Göran Svensson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115516526</v>
+        <v>115516300</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>56720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2796,20 +2805,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103042</v>
+        <v>102954</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2826,7 +2835,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2901,17 +2910,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per-Göran Svensson</t>
+          <t>Per-Göran Svensson, Jan Ottosson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115516506</v>
+        <v>123691640</v>
       </c>
       <c r="B20" t="n">
-        <v>56478</v>
+        <v>58169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2924,34 +2933,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2994,27 +2999,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mellanvägen stod på vägen.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per-Göran Svensson</t>
+          <t>Per-Göran Svensson, Tommy  Carlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115516300</v>
+        <v>123691696</v>
       </c>
       <c r="B21" t="n">
-        <v>56720</v>
+        <v>56834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102954</v>
+        <v>100065</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3074,18 +3074,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3123,22 +3115,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3158,250 +3150,10 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per-Göran Svensson, Jan Ottosson</t>
+          <t>Per-Göran Svensson, Tommy  Carlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>123691696</v>
-      </c>
-      <c r="B22" t="n">
-        <v>56833</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100065</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Grus grus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Ebbegärde Kronopark, Ebbegärde Kronopark, Sm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>574797</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6303215</v>
-      </c>
-      <c r="S22" t="n">
-        <v>50</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Ryssby</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Per-Göran Svensson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Per-Göran Svensson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>123691640</v>
-      </c>
-      <c r="B23" t="n">
-        <v>58168</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Ebbegärde Kronopark, Ebbegärde Kronopark, Sm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>574797</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6303215</v>
-      </c>
-      <c r="S23" t="n">
-        <v>50</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Ryssby</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Per-Göran Svensson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Per-Göran Svensson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -2917,10 +2917,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123691640</v>
+        <v>123691696</v>
       </c>
       <c r="B20" t="n">
-        <v>58169</v>
+        <v>56834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>100065</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2950,18 +2950,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3041,10 +3033,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123691696</v>
+        <v>123691640</v>
       </c>
       <c r="B21" t="n">
-        <v>56834</v>
+        <v>58169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3057,16 +3049,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100065</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3074,10 +3066,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>

--- a/artfynd/A 12926-2024 artfynd.xlsx
+++ b/artfynd/A 12926-2024 artfynd.xlsx
@@ -2917,10 +2917,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123691696</v>
+        <v>123691640</v>
       </c>
       <c r="B20" t="n">
-        <v>56834</v>
+        <v>58169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100065</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2950,10 +2950,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3033,10 +3041,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123691640</v>
+        <v>123691696</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>56834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3049,16 +3057,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>100065</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3066,18 +3074,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
